--- a/Result/profitability/2630.xlsx
+++ b/Result/profitability/2630.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="N2" t="n">
-        <v>10.2475</v>
+        <v>10.185</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28875</v>
+        <v>0.27625</v>
       </c>
       <c r="N3" t="n">
-        <v>10.82125</v>
+        <v>10.73875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>0.39625</v>
+        <v>0.3825</v>
       </c>
       <c r="N4" t="n">
-        <v>12.02875</v>
+        <v>11.875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.42375</v>
+        <v>0.3775</v>
       </c>
       <c r="N5" t="n">
-        <v>12.65125</v>
+        <v>12.06625</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.335</v>
+        <v>0.29625</v>
       </c>
       <c r="N6" t="n">
-        <v>12.24625</v>
+        <v>11.8125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.34375</v>
+        <v>0.3325</v>
       </c>
       <c r="N7" t="n">
-        <v>12.61125</v>
+        <v>12.54</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7675,6 +7675,133 @@
       </c>
       <c r="AM57" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>999</v>
+      </c>
+      <c r="D58" t="n">
+        <v>921</v>
+      </c>
+      <c r="E58" t="n">
+        <v>78</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="G58" t="n">
+        <v>15</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="N58" t="n">
+        <v>9.36125</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-0.1427003293084522</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-0.925</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-4.680000000000001</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>-0.3746997598078463</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
